--- a/output/pdf_financials_xlsx/WCU.xlsx
+++ b/output/pdf_financials_xlsx/WCU.xlsx
@@ -5952,43 +5952,43 @@
         <v>0.109725</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.109725</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.109725</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.109725</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.109725</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.109725</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.109725</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.109725</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.109725</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.441575</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.343305</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.454238</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.667107</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.081041</v>
       </c>
     </row>
     <row r="93">
@@ -10360,7 +10360,11 @@
           <t>Share-based payment reserves (Notes 9 and 10)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -11780,7 +11784,11 @@
           <t>Share-based payment reserves (Notes 10 and 11)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -12693,7 +12701,11 @@
           <t>Share-based payment reserves (Notes 10, 11, and 12)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -14012,7 +14024,11 @@
           <t>Share-based payment reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -14600,7 +14616,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -16338,7 +16358,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -17021,7 +17045,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WCU.xlsx
+++ b/output/pdf_financials_xlsx/WCU.xlsx
@@ -1071,7 +1071,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.007839</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
@@ -2013,7 +2013,7 @@
         <v>-16.447294</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-3.622704</v>
+        <v>-3.630543</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>-27.282563</v>
@@ -2129,7 +2129,7 @@
         <v>-16.442288</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.617725</v>
+        <v>-3.625564</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>-27.276263</v>
@@ -2394,55 +2394,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.314787</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.098283</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.54426</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.451437</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.385951</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.007557</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000111</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.000119</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.7e-05</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.000276</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>6e-05</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.32174</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.007409</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.014329</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.193977</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>2.727737</v>
       </c>
     </row>
     <row r="35">
@@ -2510,55 +2510,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.314787</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.098283</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.54426</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.451437</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.385951</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.007557</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000111</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.000119</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>3.7e-05</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.000276</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>6e-05</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.32174</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5674090000000001</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.014329</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.193977</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.85</v>
+        <v>4.577737</v>
       </c>
     </row>
     <row r="37">
@@ -3206,13 +3206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.314787</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.098283</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.54426</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -3242,19 +3242,19 @@
         <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.865026</v>
+        <v>0.543286</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.453679</v>
+        <v>0.44627</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.153559</v>
+        <v>0.13923</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>20.953659</v>
+        <v>20.759682</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>2.750315</v>
+        <v>0.022578</v>
       </c>
     </row>
     <row r="49">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -15499,7 +15499,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -34635,7 +34635,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">

--- a/output/pdf_financials_xlsx/WCU.xlsx
+++ b/output/pdf_financials_xlsx/WCU.xlsx
@@ -4387,37 +4387,37 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.012313</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.037525</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.008451</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.01288</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.02754</v>
       </c>
       <c r="N67" s="3" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q115" s="3" t="n">
         <v>0</v>
@@ -22122,7 +22122,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
